--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/4306-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/4306-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1651AC49-D7D7-4AD3-BDDC-85968582DC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{59BFF9E4-1F5D-4A40-ACEA-69D5540ADB8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{E010C607-0297-4539-B908-32C7F62618B5}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{5BCC2B19-AEDC-4F70-8586-D957784E85E4}"/>
   </bookViews>
   <sheets>
     <sheet name="4306-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1574,27 +1574,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5791FF71-0AED-4CB8-8677-172D061EDC58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C230C03-A62D-426A-B57B-7280CBEB9E60}">
   <dimension ref="A1:X39"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1628,7 +1627,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1664,7 +1663,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1716,7 +1715,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1784,7 +1783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1856,7 +1855,7 @@
         <v>9.4499999999999993</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1928,7 +1927,7 @@
         <v>5.94</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -2000,7 +1999,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2072,7 +2071,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="41">
         <v>2020</v>
       </c>
@@ -2144,7 +2143,7 @@
         <v>8.57</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="43"/>
       <c r="B10" s="44"/>
       <c r="C10" s="18" t="s">
@@ -2172,7 +2171,7 @@
       <c r="W10" s="50"/>
       <c r="X10" s="46"/>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="39">
         <v>2019</v>
       </c>
@@ -2244,7 +2243,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2018</v>
       </c>
@@ -2316,7 +2315,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <v>2017</v>
       </c>
@@ -2388,7 +2387,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2016</v>
       </c>
@@ -2460,7 +2459,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>2015</v>
       </c>
@@ -2532,7 +2531,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2014</v>
       </c>
@@ -2604,7 +2603,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>2013</v>
       </c>
@@ -2676,7 +2675,7 @@
         <v>9.5299999999999994</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2012</v>
       </c>
@@ -2748,7 +2747,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2011</v>
       </c>
@@ -2820,7 +2819,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2010</v>
       </c>
@@ -2892,7 +2891,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2009</v>
       </c>
@@ -2964,7 +2963,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2008</v>
       </c>
@@ -3036,7 +3035,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>2007</v>
       </c>
@@ -3108,7 +3107,7 @@
         <v>7.33</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="41">
         <v>2006</v>
       </c>
@@ -3180,7 +3179,7 @@
         <v>9.2799999999999994</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="43"/>
       <c r="B25" s="44"/>
       <c r="C25" s="18" t="s">
@@ -3208,7 +3207,7 @@
       <c r="W25" s="50"/>
       <c r="X25" s="46"/>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2005</v>
       </c>
@@ -3280,7 +3279,7 @@
         <v>7.33</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="41">
         <v>2004</v>
       </c>
@@ -3352,7 +3351,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="43"/>
       <c r="B28" s="44"/>
       <c r="C28" s="18" t="s">
@@ -3380,7 +3379,7 @@
       <c r="W28" s="50"/>
       <c r="X28" s="46"/>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="51">
         <v>2003</v>
       </c>
@@ -3452,7 +3451,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="53"/>
       <c r="B30" s="54"/>
       <c r="C30" s="20" t="s">
@@ -3480,7 +3479,7 @@
       <c r="W30" s="60"/>
       <c r="X30" s="56"/>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2002</v>
       </c>
@@ -3552,7 +3551,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="51">
         <v>2001</v>
       </c>
@@ -3624,7 +3623,7 @@
         <v>9.26</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="53"/>
       <c r="B33" s="54"/>
       <c r="C33" s="20" t="s">
@@ -3652,7 +3651,7 @@
       <c r="W33" s="60"/>
       <c r="X33" s="56"/>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="41">
         <v>2000</v>
       </c>
@@ -3724,7 +3723,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="43"/>
       <c r="B35" s="44"/>
       <c r="C35" s="18" t="s">
@@ -3752,7 +3751,7 @@
       <c r="W35" s="50"/>
       <c r="X35" s="46"/>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>1999</v>
       </c>
@@ -3824,7 +3823,7 @@
         <v>8.06</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>1998</v>
       </c>
@@ -3896,7 +3895,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <v>1997</v>
       </c>
@@ -3968,7 +3967,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37" t="s">
         <v>60</v>
       </c>
